--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -1,34 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dc858\Documents\Projects\RBF-FD-Elliptic\Results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC07FCB-7FF7-43B6-B289-180466A8EE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+  <si>
+    <t>Nx</t>
+  </si>
+  <si>
+    <t>Ny</t>
+  </si>
+  <si>
+    <t>num_stencil_nodes</t>
+  </si>
+  <si>
+    <t>num_rings</t>
+  </si>
+  <si>
+    <t>eigenvalue 1</t>
+  </si>
+  <si>
+    <t>eigenvalue 2</t>
+  </si>
+  <si>
+    <t>radian = r/24</t>
+  </si>
+  <si>
+    <t>augmentation</t>
+  </si>
+  <si>
+    <t>sparse</t>
+  </si>
+  <si>
+    <t>max_error_rel</t>
+  </si>
+  <si>
+    <t>l2_error_rel</t>
+  </si>
+  <si>
+    <t>energy_error_rel</t>
+  </si>
+  <si>
+    <t>varied_param</t>
+  </si>
+  <si>
+    <t>varied_value</t>
+  </si>
+  <si>
+    <t>N_int</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,81 +136,1148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>max err</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Grid Size'!$N$2:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Grid Size'!$J$10:$J$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2.2084725848693947</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7786352271349444</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.64148738331886046</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43584157152851594</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40423924252446991</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.32612398545981192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.18880621277185297</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CB92-425F-8ECC-664BB700298C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>l2 err</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Grid Size'!$N$2:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Grid Size'!$K$10:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.2562841356958159</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.60474629674767133</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.4996262590899721E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.14176743208178555</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.21537662850004188</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.29370362533611855</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.35987551424866582</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CB92-425F-8ECC-664BB700298C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>energy err</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Grid Size'!$N$2:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Grid Size'!$L$10:$L$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.93243203506960304</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72722807161550984</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.32303505131683019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.49354482776345138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.42624761610192702</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.51573210557081228</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.58863129263819503</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CB92-425F-8ECC-664BB700298C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="205509616"/>
+        <c:axId val="16731184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="205509616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="16731184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="16731184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="205509616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>140970</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>140970</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DBC2BEB-2901-9284-E076-AA7D74A919C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,106 +1564,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nx</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ny</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>num_stencil_nodes</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>num_rings</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>eigenvalue 1</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eigenvalue 2</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>radian = r/24</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>augmentation</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sparse</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>max_error_rel</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>l2_error_rel</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>energy_error_rel</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>varied_param</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>varied_value</t>
-        </is>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>20</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>20</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G2">
         <v>12</v>
       </c>
       <c r="H2" t="b">
@@ -516,44 +1640,42 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>161.6116204466646</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>18.04197745082746</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>8.559177543591165</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2">
         <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>30</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>30</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>100</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G3">
         <v>12</v>
       </c>
       <c r="H3" t="b">
@@ -562,44 +1684,42 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>60.06690112948126</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.024818464776576</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5.336150521586992</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+      <c r="J3">
+        <v>60.066901129481259</v>
+      </c>
+      <c r="K3">
+        <v>4.0248184647765761</v>
+      </c>
+      <c r="L3">
+        <v>5.3361505215869922</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>50</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>50</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G4">
         <v>12</v>
       </c>
       <c r="H4" t="b">
@@ -608,44 +1728,42 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>4.380133862665629</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9965529377382082</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.4752968638314523</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+      <c r="J4">
+        <v>4.3801338626656294</v>
+      </c>
+      <c r="K4">
+        <v>0.99655293773820819</v>
+      </c>
+      <c r="L4">
+        <v>0.47529686383145231</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4">
         <v>50</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>75</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>75</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>100</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G5">
         <v>12</v>
       </c>
       <c r="H5" t="b">
@@ -654,44 +1772,42 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>2.727982446815338</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.7214937410035708</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.3209631489784419</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+      <c r="K5">
+        <v>0.72149374100357078</v>
+      </c>
+      <c r="L5">
+        <v>0.32096314897844191</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5">
         <v>75</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>100</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>100</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>10</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G6">
         <v>12</v>
       </c>
       <c r="H6" t="b">
@@ -700,44 +1816,42 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>2.536525557434623</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.6090085242988724</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.3747592696454148</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
+      <c r="K6">
+        <v>0.60900852429887242</v>
+      </c>
+      <c r="L6">
+        <v>0.37475926964541478</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6">
         <v>100</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>125</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>100</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>10</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G7">
         <v>12</v>
       </c>
       <c r="H7" t="b">
@@ -746,44 +1860,42 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
-        <v>2.118965986299876</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.5085063430870039</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3049775662783035</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
+      <c r="J7">
+        <v>2.1189659862998762</v>
+      </c>
+      <c r="K7">
+        <v>0.50850634308700393</v>
+      </c>
+      <c r="L7">
+        <v>0.30497756627830352</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7">
         <v>125</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>150</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>150</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>100</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>10</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G8">
         <v>12</v>
       </c>
       <c r="H8" t="b">
@@ -792,25 +1904,104 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>1.544565082920097</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.4366409726514244</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2578509331058249</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N_int</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+      <c r="K8">
+        <v>0.43664097265142437</v>
+      </c>
+      <c r="L8">
+        <v>0.25785093310582491</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8">
         <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J10" cm="1">
+        <f t="array" ref="J10:J16">LOG10(J2:J8)</f>
+        <v>2.2084725848693947</v>
+      </c>
+      <c r="K10" cm="1">
+        <f t="array" ref="K10:K16">LOG10(K2:K8)</f>
+        <v>1.2562841356958159</v>
+      </c>
+      <c r="L10" cm="1">
+        <f t="array" ref="L10:L16">LOG10(L2:L8)</f>
+        <v>0.93243203506960304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>1.7786352271349444</v>
+      </c>
+      <c r="K11">
+        <v>0.60474629674767133</v>
+      </c>
+      <c r="L11">
+        <v>0.72722807161550984</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>0.64148738331886046</v>
+      </c>
+      <c r="K12">
+        <v>-1.4996262590899721E-3</v>
+      </c>
+      <c r="L12">
+        <v>-0.32303505131683019</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>0.43584157152851594</v>
+      </c>
+      <c r="K13">
+        <v>-0.14176743208178555</v>
+      </c>
+      <c r="L13">
+        <v>-0.49354482776345138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>0.40423924252446991</v>
+      </c>
+      <c r="K14">
+        <v>-0.21537662850004188</v>
+      </c>
+      <c r="L14">
+        <v>-0.42624761610192702</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>0.32612398545981192</v>
+      </c>
+      <c r="K15">
+        <v>-0.29370362533611855</v>
+      </c>
+      <c r="L15">
+        <v>-0.51573210557081228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>0.18880621277185297</v>
+      </c>
+      <c r="K16">
+        <v>-0.35987551424866582</v>
+      </c>
+      <c r="L16">
+        <v>-0.58863129263819503</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -813,4 +814,642 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7.217390878761201</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.719470169988806</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.261939104123757</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.466943116863774</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.356080594545402</v>
+      </c>
+      <c r="L3" t="n">
+        <v>50.40831391681537</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.061396486058499</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.370272530535686</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.0548840134392</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.534368594743643</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.081698014931554</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4189754297353431</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.408912479644637</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.039531713549335</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4384069402013412</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.01983970310142</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7328528110597742</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3706716362547848</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.095104251354071</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.048957038005857</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.81919148711479</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.536525557434623</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6090085242988724</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3747592696454148</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.700778075700205</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6110750123904181</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3968694471170766</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.121499395786802</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7785042725700748</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.308206392395286</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>196.8648137350137</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.200429203005752</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.708455217259043</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>403.890257601675</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24.90844522282582</v>
+      </c>
+      <c r="L13" t="n">
+        <v>90929.51105840236</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1452,4 +1453,458 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>916.4904065807923</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.92198123881208</v>
+      </c>
+      <c r="L2" t="n">
+        <v>26986573.34286742</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1000.584331839379</v>
+      </c>
+      <c r="K3" t="n">
+        <v>55.76590551161239</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2417.298391781507</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3919.340010618429</v>
+      </c>
+      <c r="K4" t="n">
+        <v>180.3499463555513</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4751.156539630079</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.59695857762125</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.478034166212935</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.444896389660316</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.534635665516181</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6531334106813781</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4095097568227352</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.536525557434623</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6090085242988724</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3747592696454148</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.532203788444122</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5838122077936986</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.608995544141795</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.554728301878214</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.579242302507944</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3431650799217577</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1907,4 +1908,688 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.007987020418409093</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.002477005975992475</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.006764465472416281</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.008234228610848675</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.002483313145233347</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.004761193207318502</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01022416124622196</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002956477646171381</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.002598419975513143</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.01894530063965734</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.004298974829685423</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.002294102231516923</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.05487561316785517</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.01669469497869046</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.007956199175840183</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0923513228536782</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.03403464205478025</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01650587970281754</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9835780744560698</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2640118171057566</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1383627571095477</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.536525557434623</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6090085242988724</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3747592696454148</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.42070953607521</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.627316411706854</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.551897583446733</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>59.72227727066409</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20.6047462912363</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.332544522899114</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1480.814203138928</v>
+      </c>
+      <c r="K12" t="n">
+        <v>498.9175830788438</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.26473576703101</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1118.583673437739</v>
+      </c>
+      <c r="K13" t="n">
+        <v>288.3597074716018</v>
+      </c>
+      <c r="L13" t="n">
+        <v>48.67109660260322</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1649.082454660343</v>
+      </c>
+      <c r="K14" t="n">
+        <v>463.3788168280367</v>
+      </c>
+      <c r="L14" t="n">
+        <v>63.25320754252024</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2592,4 +2593,504 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.00880797928060704</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.002523984817953004</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03367476988352975</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.009224048870431161</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.002526409994922472</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7623578325175421</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01053054690622822</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002980602213658026</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3159532838414529</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.02523135183275443</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.005667660619503539</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.04207316250829357</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.536525557434623</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6090085242988724</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3747592696454148</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.02343618324915642</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.005665517808219538</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01821871457938391</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01000261245178448</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.002979681779216079</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0887021596243978</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.009140939341778365</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002525696526503021</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5496537497034916</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008807979280748612</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00252398481795667</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03367476988425203</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10958.46902261261</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8636.596276831569</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11260.98260824322</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.07208425881611</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.266471180683159</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11141.26331908642</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8800.465787609955</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11208.61419704283</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.07164018720006</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.266342562607703</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11.08964708941122</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8.534328206924544</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28.16381333827857</v>
+      </c>
+      <c r="N14" t="n">
+        <v>26.85850944045401</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.296698363859547</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.608350966673075</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.693974665201448</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8.169980251756666</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.271998722670155</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.003306282733225</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>41.45310997952264</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27.17785730196401</v>
+      </c>
+      <c r="M16" t="n">
+        <v>79.76090502866921</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.129271526954923</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.861267840506698</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.172828056530742</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.680444486688706</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10.84879609213974</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.407653563077067</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.6647772618793294</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.245566295641344</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.085913427848538</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.863676559848112</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.552065186075419</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8547256552622455</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.3033293604884074</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1878696896559005</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8068877299080194</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.20164430346312</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3404232307468261</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.4087782640865146</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2318922955750363</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.814425093549773</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.452305301143351</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.1379381882027332</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1629884370408964</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.09045349569075072</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5379146214378717</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.9146778205089545</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1224296725748649</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.02326189163166523</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.008130036335756602</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.08805840340816523</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.04320203977848805</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.01963982024175665</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.01222168271156467</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.007872163681152677</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.2959516948224924</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.04578796406534415</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.00616132624895982</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.002672241353134167</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0007106929273409949</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3162813211807338</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.2070991428308552</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.01682882876268451</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.511487311481613</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6729466751188072</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.902054113569692</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2464620922985615</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05125995828059593</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2990151426765247</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1033606554160341</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.196821631500364</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7532927992647811</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07522744255496674</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.279457511197636</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2081148426200317</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9250225932981868</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8417207800857439</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2620981745268057</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.144631615046016</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0615627530302894</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.47116944618421</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.212785195865682</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1924036576177718</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.08470605861301288</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.06066734441852201</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3204840858798986</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.882208485135335</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2325126124743113</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3492711093864515</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2902525520492159</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.3303085141073</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.271747828970681</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2685195749295496</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.010164197869604</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5630636793342838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.378028855567108</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.45493159332162</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.275056761481844</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.245566295641344</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.085913427848538</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.863676559848112</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.552065186075419</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8547256552622455</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.228738950683492</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.602482537269306</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.009609773089393</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.559937943966081</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.6763697179257266</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8326487981983336</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6722015643674061</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.647080799875303</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.334429780161648</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5245603410412918</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7408208771155644</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6680047408302821</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.184420851238715</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.17221572641153</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.016418385785061</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8803737975434688</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5992068084043852</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.758323607880804</v>
+      </c>
+      <c r="N13" t="n">
+        <v>17.72731811653708</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.111022355191747</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.233107324590565</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.002687553604013</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15.39838348989492</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.987376116222714</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.069829807893833</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.151121612092308</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.955706763327401</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.21937006348307</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.987547431069789</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.069984944950633</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6931075837979852</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.580397228261194</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.12141155404173</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.309214935376325</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6277808004718685</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.006163737606822</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.688268786953035</v>
+      </c>
+      <c r="M5" t="n">
+        <v>29.37069538220079</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.356358190340099</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6224752643428131</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1161983787553147</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.07827042993104071</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4963281252134678</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5416625646038711</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1486894622520221</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1256348797666301</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.08543738103193087</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5169666157702164</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5456361732011051</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1486440781703947</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1306188944771273</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.05969940218231806</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3687350101944615</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.345007573972035</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1730374374839978</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.07328779849141831</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.05058180687546747</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2795432292045207</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8703784869624174</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2027171857371205</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01487570340595509</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01095142789063473</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0542012286041837</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2004701884198049</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.08646967818696864</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02397622491148601</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01571640770799104</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.07819667552401514</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.09037905518911318</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06718333116346484</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01940492719791077</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.004781062603733436</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.8277755045757629</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.413907283899319</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3149710981084763</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.002830991233286571</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0008306679653230766</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.04743380081727538</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.664086477811896</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08881125175523234</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0004728738236380784</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0004405405193408491</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01793664964286452</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2981783532062746</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.03584185723160366</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.005521952557073358</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.004786553849920933</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.08014133607996923</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.20322741739014</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.6483152701988218</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1209613899385818</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.114120250685791</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3579293685083496</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20.16030726003029</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.953833749100085</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1985,1526 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.353093648965124</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2466187680857859</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.779401907746599</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.557583470787879</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1077008291310017</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02661001349002958</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.009921507887459071</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.08896279289064186</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7001754352587769</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1022569160974853</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02664455623506811</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02368186484593616</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1702846784444131</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7999511333972835</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.09521162142898384</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04320376538336138</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01853460445377481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.09054270998586858</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.301079806399367</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.250428196198912</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.472622225314715</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9279419586302103</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.709677695082165</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.498629542261587</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3633427483611797</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4423055655796947</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3222356295157361</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.900829164247645</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.009328325455538</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3136820312664732</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1862635328444485</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1066181754877096</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7017041346797238</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6824170454622508</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1684068651569113</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.06676533188119563</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03866626785027929</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4965167449288382</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.165224204277729</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1428886482666861</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.414033318200856</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.799506270254379</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14.94420175138358</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.768719394498668</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2004475686885513</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0699783074267827</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.04734244042131276</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2171940361420681</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.665488572149173</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.2338036818919892</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3487648778953194</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1939375826119603</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7445742199098498</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.501513373772502</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.2226303641065009</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1260410658297057</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.09453126511035355</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3852030323166729</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.417645197341876</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4227185491418483</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.126546101097189</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.463233913125397</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.798522583078377</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.066559932782329</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9077935559692039</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.560091879051564</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.073686136230194</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.324233128725358</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7.932671371403623</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.8079544495051445</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03028596714295725</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.02336989406454065</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3034038924579883</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.07883575404274562</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06436491454914577</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03437053285191969</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.02356737330888665</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2738368950419379</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07883825679758219</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.06437587254118515</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.03900911531348537</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02578972528022792</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3157303498085456</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0788373604838097</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.06437934988432205</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03494645682289303</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.02394007509839936</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2846243039382761</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.07883359474374736</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06438076328697416</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03399437959829742</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.02330356121841276</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2701675833174839</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.07883389376823907</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06439123167740288</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.01890141736524103</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.01204045459178352</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.08202147680028025</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2002161661236625</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.08515591657561143</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01746198972655891</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.01182443066993654</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.07502441220806268</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2004294318328799</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08523853363665862</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01487570340595509</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01095142789063473</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0542012286041837</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2004701884198049</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.08646967818696864</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02580093710180688</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01736362814174261</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1831388405294319</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4457355136338344</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.09691209553704598</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.04298066264071009</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0252844486504095</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2212409981880693</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3327372701982303</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.09577608742380565</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0004405546527635527</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0004415028513791253</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002262567151354062</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0002102157376115121</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7.864700047585245e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001220448257265651</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.000118440494244478</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.00011637250746382</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0001954353636974877</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7.424980166435159e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.057339653217078e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.909529451031967e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.800405628469402e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.000130738569288985</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6.643142218282081e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.160551689022813e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.932056413391929e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.285653453108498e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001544410165954567</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8.654768426878586e-05</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.389835881356549e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.034054772012819e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001389586198266056</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0003157643069939576</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0001316836746075014</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.868447598767258e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.196239749568147e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001826561561586858</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0005209333874926904</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0001919408356483257</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02700689738835117</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.009916950085468409</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1564629883992069</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03245624619239457</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01201583347126995</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01487570340595509</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01095142789063473</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0542012286041837</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2004701884198049</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.08646967818696864</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.574456975242367</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.455673950854714</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22.56764161582908</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.675072258461038</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.694669375329931</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.31383059372327</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.615618550538786</v>
+      </c>
+      <c r="M11" t="n">
+        <v>41.70996958734718</v>
+      </c>
+      <c r="N11" t="n">
+        <v>43.39978492014818</v>
+      </c>
+      <c r="O11" t="n">
+        <v>20.76420809473305</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19.10326057347921</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.59445041193471</v>
+      </c>
+      <c r="M12" t="n">
+        <v>107.0463951568874</v>
+      </c>
+      <c r="N12" t="n">
+        <v>644.4852991515187</v>
+      </c>
+      <c r="O12" t="n">
+        <v>375.5880842541187</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>14.05862566418408</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.2914457690925</v>
+      </c>
+      <c r="M13" t="n">
+        <v>339.0357416990777</v>
+      </c>
+      <c r="N13" t="n">
+        <v>211.5847352988328</v>
+      </c>
+      <c r="O13" t="n">
+        <v>219.7314060532517</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>31.25347335689719</v>
+      </c>
+      <c r="L14" t="n">
+        <v>47.71786959224197</v>
+      </c>
+      <c r="M14" t="n">
+        <v>220.7271387977152</v>
+      </c>
+      <c r="N14" t="n">
+        <v>503.437387274801</v>
+      </c>
+      <c r="O14" t="n">
+        <v>348.9740314807043</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_10.xlsx
+++ b/Results/rbf_fd_parameter_study_10.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0168663424869658</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.02329848237951891</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.001512961217305976</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001379741828889676</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.518039280236263e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0007243867161968131</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0006118603160133836</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0006001533996387123</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0001330499312285429</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.638495090177143e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001086021265897762</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.540368869382393e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001191145318189447</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0001436678661172693</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6.688659261348919e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.34957636221553e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.966398595151366e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001524286846490227</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0002073912264311897</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0001093724597129587</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.01487570340595509</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01095142789063473</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0542012286041837</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2004701884198049</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.08646967818696864</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.426949488456823e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.752020797892694e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001303078242930646</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0002080892908314005</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.000110377273457031</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.159737248402091e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.748436471560024e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9.773434397572599e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001450257136052292</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.738637942526579e-05</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0005300330227715563</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0003232960069559356</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0003254166783979569</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0001334038776401024</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.660568315648559e-05</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01686634013208413</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.02329848090778061</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001512961110719213</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001379741828261097</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.518039271346825e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>